--- a/markdown_generator/students.xlsx
+++ b/markdown_generator/students.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$G$15</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,47 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F4F8F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEEFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDFFDD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFADD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE8DD"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -80,63 +46,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,17 +427,8 @@
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -552,498 +465,497 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Wentao Deng</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Shandong University</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Legal Dialogue Generation and Reasoning with Large Language Models (Research)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>01/09/2022</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Yuanxing Liu</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>University of Amsterdam</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Conversational Recommendation (Research)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01/07/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Weijia Zhang</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>University of Amsterdam</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Faithfulness Evaluation of Large Language Models (Research)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Xin Sun</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>University of Amsterdam / Centrum Wiskunde &amp; Informatica</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>From Aligned Models to Trusted Interfaces: Explainable Health Intervention and Transparent Health Information Seeking (Research)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>01/09/2024</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Qingyu Meng</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Trustworthy Multi-Agents and Safety Alignment</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="2" t="n">
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Yifan Mo</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Psycholinguistic Bonding in Conversational Agents</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Yue Su</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Gaze Perception and Understanding Beyond Conversations</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15/11/2025</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="5" t="n">
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Arent Stienstra</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>University of Amsterdam, Informatics Institute</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Role-aware Recurrent Entity Networks for Task-oriented Dialogue Systems (Thesis)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>2018-03-19</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>2018-09-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>19/03/2018</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>19/09/2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Basak Tugce Eskili</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>University of Amsterdam, Informatics Institute</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hierarchical Merchant Category Code Assignment for E-commerce Merchants (Thesis)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>2019-01-26</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>2019-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>26/01/2019</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>26/05/2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Guojun Yan</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Shandong University</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Medical Dialogue Agents (Research)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>2022-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01/06/2021</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01/06/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Chengshun Shi</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Shandong University</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Efficient Fine-tuning for Large Language Models</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>01/06/2023</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Haochen Huang</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>University of Amsterdam / Vrije Universiteit Amsterdam / Centrum Wiskunde &amp; Informatica</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Fine-Grained Vision-Language Modeling for Multimodal Training Assistants in Augmented Reality (Thesis, Nominated for Amsterdam AI Thesis Awards)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>15/01/2024</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>15/07/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Tyler Cools</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>University of Amsterdam, Informatics Institute</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Using Source Awareness in Memory End-to-End Task-oriented Dialog Learning (Thesis)</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>2018-12-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="11" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>12/06/2018</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>12/12/2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Albert Tang</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>High School</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Marriotts Ridge High School</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Human-Centered AI for Neurodiverse Communication</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/students.xlsx
+++ b/markdown_generator/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DD35F0-CEC9-1C4C-A0C3-01849D5CDA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF0BAD3-623F-3C46-B4A5-BDB28C8A3DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="107">
   <si>
     <t>#</t>
   </si>
@@ -91,9 +91,6 @@
     <t>University of Amsterdam / Centrum Wiskunde &amp; Informatica</t>
   </si>
   <si>
-    <t>From Aligned Models to Trusted Interfaces: Explainable Health Intervention and Transparent Health Information Seeking (Research)</t>
-  </si>
-  <si>
     <t>01/09/2024</t>
   </si>
   <si>
@@ -227,13 +224,130 @@
   </si>
   <si>
     <t>25/10/2025</t>
+  </si>
+  <si>
+    <t>Psycholinguistic Dialogue Generation (Research)</t>
+  </si>
+  <si>
+    <t>Mithat Can Ozgun</t>
+  </si>
+  <si>
+    <t>15/10/2024</t>
+  </si>
+  <si>
+    <t>18/06/2025</t>
+  </si>
+  <si>
+    <t>Xiao Fu</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>15/08/2025</t>
+  </si>
+  <si>
+    <t>Dingming Liu</t>
+  </si>
+  <si>
+    <t>Trustworthy AI Psychotherapy: Multi-Agent LLM Workflow for Counseling and Explainable Mental Disorder Diagnosis (Thesis =&gt; CIKM25)</t>
+  </si>
+  <si>
+    <t>Multi-Agent Simulation of Client-Therapist Dialogues with Large Language Models: An MI-Centered Framework (Thesis =&gt; ACL26)</t>
+  </si>
+  <si>
+    <t>Evaluating Mathematical Reasoning Abilities of Large Language Models within Scientific Literature (Thesis =&gt; ACL26)</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>10/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yas Lotfi </t>
+  </si>
+  <si>
+    <t>Explainable Conversational Agent for Mental Health Chatbots Using LLMs</t>
+  </si>
+  <si>
+    <t>17/01/2025</t>
+  </si>
+  <si>
+    <t>25/06/2025</t>
+  </si>
+  <si>
+    <t>Design, Implementation and Evaluation of Vision and Language Agents for LEGO Assembly in Augmented Reality</t>
+  </si>
+  <si>
+    <t>Mkita Yurchyk</t>
+  </si>
+  <si>
+    <t>08/04/2025</t>
+  </si>
+  <si>
+    <t>27/11/2025</t>
+  </si>
+  <si>
+    <t>Thomas Glatz</t>
+  </si>
+  <si>
+    <t>Digital Employee with LLMs</t>
+  </si>
+  <si>
+    <t>07-10-2025</t>
+  </si>
+  <si>
+    <t>Hristina Chalokova</t>
+  </si>
+  <si>
+    <t>19-11-2025</t>
+  </si>
+  <si>
+    <t>Soften Resistance in LLM Mental Health Agents</t>
+  </si>
+  <si>
+    <t>Jiaqi Shi</t>
+  </si>
+  <si>
+    <t>Real-Time Cognitive Load Classification for Adaptive Online Learning Systems</t>
+  </si>
+  <si>
+    <t>17/12/2025</t>
+  </si>
+  <si>
+    <t>Chi Zhang</t>
+  </si>
+  <si>
+    <t>Pre-play – visual communication for everyday autistic life</t>
+  </si>
+  <si>
+    <t>14/01/2026</t>
+  </si>
+  <si>
+    <t>Marouan Hmidach</t>
+  </si>
+  <si>
+    <t>Learning-to-Ask Agent for Structured Report Generation in Special Education</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>Jason Wang</t>
+  </si>
+  <si>
+    <t>Gaze Language Models for Mental Health Support</t>
+  </si>
+  <si>
+    <t>02-12-2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +359,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -283,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -299,6 +419,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -602,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
@@ -610,8 +742,8 @@
     <col min="3" max="3" width="10.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="46.1640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13" style="6" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="6" customWidth="1"/>
     <col min="8" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
@@ -631,10 +763,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
@@ -654,10 +786,10 @@
       <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -677,10 +809,10 @@
       <c r="E3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -700,14 +832,14 @@
       <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -721,13 +853,13 @@
         <v>22</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -735,22 +867,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -758,22 +890,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>30</v>
+      <c r="G7" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -781,22 +913,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>30</v>
+      <c r="G8" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -804,22 +936,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -827,22 +959,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -850,22 +982,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -873,21 +1005,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -896,22 +1028,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -919,22 +1051,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -942,22 +1074,275 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>30</v>
+      <c r="G15" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/students.xlsx
+++ b/markdown_generator/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF0BAD3-623F-3C46-B4A5-BDB28C8A3DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7679E69A-3182-0E43-93A6-8F16BF9190C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>Shandong University</t>
   </si>
   <si>
-    <t>Legal Dialogue Generation and Reasoning with Large Language Models (Research)</t>
-  </si>
-  <si>
     <t>01/09/2022</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>University of Amsterdam</t>
   </si>
   <si>
-    <t>Conversational Recommendation (Research)</t>
-  </si>
-  <si>
     <t>01/01/2023</t>
   </si>
   <si>
@@ -103,9 +97,6 @@
     <t>Vrije Universiteit Amsterdam</t>
   </si>
   <si>
-    <t>Trustworthy Multi-Agents and Safety Alignment</t>
-  </si>
-  <si>
     <t>15/10/2025</t>
   </si>
   <si>
@@ -115,18 +106,12 @@
     <t>Yifan Mo</t>
   </si>
   <si>
-    <t>Psycholinguistic Bonding in Conversational Agents</t>
-  </si>
-  <si>
     <t>01/11/2025</t>
   </si>
   <si>
     <t>Yue Su</t>
   </si>
   <si>
-    <t>Gaze Perception and Understanding Beyond Conversations</t>
-  </si>
-  <si>
     <t>15/11/2025</t>
   </si>
   <si>
@@ -139,9 +124,6 @@
     <t>University of Amsterdam, Informatics Institute</t>
   </si>
   <si>
-    <t>Role-aware Recurrent Entity Networks for Task-oriented Dialogue Systems (Thesis)</t>
-  </si>
-  <si>
     <t>19/03/2018</t>
   </si>
   <si>
@@ -163,9 +145,6 @@
     <t>Guojun Yan</t>
   </si>
   <si>
-    <t>Medical Dialogue Agents (Research)</t>
-  </si>
-  <si>
     <t>01/06/2021</t>
   </si>
   <si>
@@ -175,9 +154,6 @@
     <t>Chengshun Shi</t>
   </si>
   <si>
-    <t>Efficient Fine-tuning for Large Language Models</t>
-  </si>
-  <si>
     <t>01/06/2023</t>
   </si>
   <si>
@@ -220,15 +196,9 @@
     <t>Marriotts Ridge High School</t>
   </si>
   <si>
-    <t>Human-Centered AI for Neurodiverse Communication</t>
-  </si>
-  <si>
     <t>25/10/2025</t>
   </si>
   <si>
-    <t>Psycholinguistic Dialogue Generation (Research)</t>
-  </si>
-  <si>
     <t>Mithat Can Ozgun</t>
   </si>
   <si>
@@ -268,18 +238,12 @@
     <t xml:space="preserve">Yas Lotfi </t>
   </si>
   <si>
-    <t>Explainable Conversational Agent for Mental Health Chatbots Using LLMs</t>
-  </si>
-  <si>
     <t>17/01/2025</t>
   </si>
   <si>
     <t>25/06/2025</t>
   </si>
   <si>
-    <t>Design, Implementation and Evaluation of Vision and Language Agents for LEGO Assembly in Augmented Reality</t>
-  </si>
-  <si>
     <t>Mkita Yurchyk</t>
   </si>
   <si>
@@ -292,9 +256,6 @@
     <t>Thomas Glatz</t>
   </si>
   <si>
-    <t>Digital Employee with LLMs</t>
-  </si>
-  <si>
     <t>07-10-2025</t>
   </si>
   <si>
@@ -304,43 +265,82 @@
     <t>19-11-2025</t>
   </si>
   <si>
-    <t>Soften Resistance in LLM Mental Health Agents</t>
-  </si>
-  <si>
     <t>Jiaqi Shi</t>
   </si>
   <si>
-    <t>Real-Time Cognitive Load Classification for Adaptive Online Learning Systems</t>
-  </si>
-  <si>
     <t>17/12/2025</t>
   </si>
   <si>
     <t>Chi Zhang</t>
   </si>
   <si>
-    <t>Pre-play – visual communication for everyday autistic life</t>
-  </si>
-  <si>
     <t>14/01/2026</t>
   </si>
   <si>
     <t>Marouan Hmidach</t>
   </si>
   <si>
-    <t>Learning-to-Ask Agent for Structured Report Generation in Special Education</t>
-  </si>
-  <si>
     <t>17/03/2026</t>
   </si>
   <si>
     <t>Jason Wang</t>
   </si>
   <si>
-    <t>Gaze Language Models for Mental Health Support</t>
-  </si>
-  <si>
     <t>02-12-2025</t>
+  </si>
+  <si>
+    <t>Efficient Fine-tuning for Large Language Models (Research=&gt;ACL24)</t>
+  </si>
+  <si>
+    <t>Medical Dialogue Agents (Research=&gt;SIGIR23)</t>
+  </si>
+  <si>
+    <t>Role-aware Recurrent Entity Networks for Task-oriented Dialogue Systems (Thesis=&gt;IJCAI SCAI Workshop)</t>
+  </si>
+  <si>
+    <t>Psycholinguistic Dialogue Generation (Research=&gt; COLING24,COLING25, CSCW25)</t>
+  </si>
+  <si>
+    <t>Conversational Recommendation (Research=&gt;TOIS25)</t>
+  </si>
+  <si>
+    <t>Legal Dialogue Generation and Reasoning with Large Language Models (Research=&gt;EMNLP23, TACL23, NeruIPS25)</t>
+  </si>
+  <si>
+    <t>Trustworthy Multi-Agents and Safety Alignment (Ongoing PhD=&gt;ACL26)</t>
+  </si>
+  <si>
+    <t>Psycholinguistic Bonding in Conversational Agents  (Ongoing PhD=&gt;ACL26, CHI26)</t>
+  </si>
+  <si>
+    <t>Gaze Perception and Understanding Beyond Conversations (Ongoing PhD=&gt;ACL26, CHI26)</t>
+  </si>
+  <si>
+    <t>Human-Centered AI for Neurodiverse Communication (Research=&gt;CHI26)</t>
+  </si>
+  <si>
+    <t>Explainable Conversational Agent for Mental Health Chatbots Using LLMs (Thesis)</t>
+  </si>
+  <si>
+    <t>Design, Implementation and Evaluation of Vision and Language Agents for LEGO Assembly in Augmented Reality (Thesis=&gt;Conference Submission)</t>
+  </si>
+  <si>
+    <t>Digital Employee with LLMs (Thesis=&gt;Conference Submission)</t>
+  </si>
+  <si>
+    <t>Soften Resistance in LLM Mental Health Agents (Thesis=&gt;Conference Submission)</t>
+  </si>
+  <si>
+    <t>Gaze Language Models for Mental Health Support (Thesis)</t>
+  </si>
+  <si>
+    <t>Real-Time Cognitive Load Classification for Adaptive Online Learning Systems (Thesis)</t>
+  </si>
+  <si>
+    <t>Learning-to-Ask Agent for Structured Report Generation in Special Education (Thesis)</t>
+  </si>
+  <si>
+    <t>Pre-play – Visual Communication for Everyday Autistic Life (Thesis)</t>
   </si>
 </sst>
 </file>
@@ -741,7 +741,7 @@
     <col min="2" max="2" width="16.1640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="46.1640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="65.83203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="79.83203125" style="5" customWidth="1"/>
     <col min="6" max="6" width="13" style="6" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" style="6" customWidth="1"/>
     <col min="8" max="16384" width="8.83203125" style="3"/>
@@ -770,7 +770,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -784,13 +784,13 @@
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -798,22 +798,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -821,22 +821,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -844,22 +844,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -867,22 +867,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -890,68 +890,68 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -959,22 +959,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="F10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="G10" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -982,22 +982,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1005,22 +1005,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1028,22 +1028,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1051,22 +1051,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1074,22 +1074,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1097,22 +1097,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1120,22 +1120,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1143,22 +1143,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1166,22 +1166,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1189,22 +1189,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1212,22 +1212,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1235,22 +1235,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1258,22 +1258,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1281,22 +1281,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1304,22 +1304,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1327,22 +1327,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/students.xlsx
+++ b/markdown_generator/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7679E69A-3182-0E43-93A6-8F16BF9190C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7944D780-FFB6-9A45-B15C-7F016F3D485F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -163,9 +163,6 @@
     <t>University of Amsterdam / Vrije Universiteit Amsterdam / Centrum Wiskunde &amp; Informatica</t>
   </si>
   <si>
-    <t>Fine-Grained Vision-Language Modeling for Multimodal Training Assistants in Augmented Reality (Thesis, Nominated for Amsterdam AI Thesis Awards)</t>
-  </si>
-  <si>
     <t>15/01/2024</t>
   </si>
   <si>
@@ -341,6 +338,9 @@
   </si>
   <si>
     <t>Pre-play – Visual Communication for Everyday Autistic Life (Thesis)</t>
+  </si>
+  <si>
+    <t>Fine-Grained Vision-Language Modeling for Multimodal Training Assistants in Augmented Reality (Thesis=&gt;Nominated for Amsterdam AI Thesis Awards, Conference Submission)</t>
   </si>
 </sst>
 </file>
@@ -784,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>10</v>
@@ -807,7 +807,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>14</v>
@@ -853,7 +853,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>21</v>
@@ -876,7 +876,7 @@
         <v>24</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>25</v>
@@ -899,7 +899,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>28</v>
@@ -922,7 +922,7 @@
         <v>24</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>30</v>
@@ -945,7 +945,7 @@
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>34</v>
@@ -991,7 +991,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>41</v>
@@ -1014,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>44</v>
@@ -1037,13 +1037,13 @@
         <v>46</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1051,22 +1051,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1074,19 +1074,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>26</v>
@@ -1097,7 +1097,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>32</v>
@@ -1106,13 +1106,13 @@
         <v>24</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1120,7 +1120,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>32</v>
@@ -1129,13 +1129,13 @@
         <v>24</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1143,7 +1143,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
@@ -1152,13 +1152,13 @@
         <v>24</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1166,22 +1166,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1189,22 +1189,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1212,7 +1212,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
@@ -1221,10 +1221,10 @@
         <v>24</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>26</v>
@@ -1235,7 +1235,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
@@ -1244,10 +1244,10 @@
         <v>24</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>26</v>
@@ -1258,7 +1258,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
@@ -1267,10 +1267,10 @@
         <v>24</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>26</v>
@@ -1281,19 +1281,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>26</v>
@@ -1304,19 +1304,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>26</v>
@@ -1327,19 +1327,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>26</v>

--- a/markdown_generator/students.xlsx
+++ b/markdown_generator/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7944D780-FFB6-9A45-B15C-7F016F3D485F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058B75B2-967F-6B44-9BF6-9196AEC93B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="120">
   <si>
     <t>#</t>
   </si>
@@ -341,13 +341,52 @@
   </si>
   <si>
     <t>Fine-Grained Vision-Language Modeling for Multimodal Training Assistants in Augmented Reality (Thesis=&gt;Nominated for Amsterdam AI Thesis Awards, Conference Submission)</t>
+  </si>
+  <si>
+    <t>Tianshi Cai</t>
+  </si>
+  <si>
+    <t>University of Liverpool</t>
+  </si>
+  <si>
+    <t>Financial Decision Credibility and Report Quality (Research=&gt;Conference Submission)</t>
+  </si>
+  <si>
+    <t>03/09/2025</t>
+  </si>
+  <si>
+    <t>Zimu Wang</t>
+  </si>
+  <si>
+    <t>09/05/2025</t>
+  </si>
+  <si>
+    <t>The Hong Kong University of Science and Technology (Guangzhou)</t>
+  </si>
+  <si>
+    <t>Wiam Osman</t>
+  </si>
+  <si>
+    <t>Tohoku University</t>
+  </si>
+  <si>
+    <t>Tian Xia</t>
+  </si>
+  <si>
+    <t>Bridging Intergenerational Communication with LLMs (Research=&gt;Conference Submission)</t>
+  </si>
+  <si>
+    <t>Adaptive Large Language Model Merging (Research=&gt;Conference Submission)</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +405,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -734,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
@@ -1345,7 +1390,100 @@
         <v>26</v>
       </c>
     </row>
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/students.xlsx
+++ b/markdown_generator/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058B75B2-967F-6B44-9BF6-9196AEC93B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E497E2-F589-2C4D-8633-F050C93DFD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,9 +73,6 @@
     <t>Weijia Zhang</t>
   </si>
   <si>
-    <t>Faithfulness Evaluation of Large Language Models (Research)</t>
-  </si>
-  <si>
     <t>01/01/2024</t>
   </si>
   <si>
@@ -292,9 +289,6 @@
     <t>Medical Dialogue Agents (Research=&gt;SIGIR23)</t>
   </si>
   <si>
-    <t>Role-aware Recurrent Entity Networks for Task-oriented Dialogue Systems (Thesis=&gt;IJCAI SCAI Workshop)</t>
-  </si>
-  <si>
     <t>Psycholinguistic Dialogue Generation (Research=&gt; COLING24,COLING25, CSCW25)</t>
   </si>
   <si>
@@ -380,6 +374,12 @@
   </si>
   <si>
     <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>Faithfulness Evaluation of Large Language Models (Research=&gt;INLG24)</t>
+  </si>
+  <si>
+    <t>Role-aware Recurrent Entity Networks for Task-oriented Dialogue Systems (Thesis=&gt;IJCAI19 SCAI Workshop)</t>
   </si>
 </sst>
 </file>
@@ -829,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>10</v>
@@ -852,7 +852,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>14</v>
@@ -875,10 +875,10 @@
         <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>11</v>
@@ -889,22 +889,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -912,22 +912,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -935,22 +935,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -958,22 +958,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -981,22 +981,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1004,22 +1004,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1027,22 +1027,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1050,19 +1050,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>11</v>
@@ -1073,22 +1073,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1096,22 +1096,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1119,22 +1119,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="G15" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1142,22 +1142,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1165,22 +1165,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1188,22 +1188,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1211,22 +1211,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1234,22 +1234,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1257,22 +1257,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1280,22 +1280,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1303,22 +1303,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="G23" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1326,22 +1326,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1349,22 +1349,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="G25" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1372,22 +1372,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="G26" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1395,22 +1395,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="F27" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="G27" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1418,22 +1418,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1441,22 +1441,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1464,22 +1464,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
